--- a/data/m3/po-numbers.xlsx
+++ b/data/m3/po-numbers.xlsx
@@ -389,93 +389,59 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
-        <v>1010047516</v>
+        <v>1010033472</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="1">
-        <v>1010047517</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="1">
-        <v>1010047519</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="1">
-        <v>1010047521</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="1">
-        <v>1010047520</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="1">
-        <v>1010047518</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="1">
-        <v>1010047522</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="1">
-        <v>1010047523</v>
-      </c>
+      <c r="A9" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="1">
-        <v>1010047525</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="1">
-        <v>1010047527</v>
-      </c>
+      <c r="A11" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="1">
-        <v>1010047526</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="1">
-        <v>1010047524</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="1">
-        <v>1010047530</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="1">
-        <v>1010047529</v>
-      </c>
+      <c r="A15" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="1">
-        <v>1010047528</v>
-      </c>
+      <c r="A16" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="1">
-        <v>1010047533</v>
-      </c>
+      <c r="A17" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="1">
-        <v>1010047532</v>
-      </c>
+      <c r="A18" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1">
-        <v>1010047531</v>
-      </c>
+      <c r="A19" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1"/>

--- a/data/m3/po-numbers.xlsx
+++ b/data/m3/po-numbers.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -35,6 +35,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -66,9 +72,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -376,10 +385,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="11.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="11.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -389,59 +398,93 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
-        <v>1010033472</v>
+        <v>1010050419</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1">
+        <v>1010050420</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>1010050421</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>1010050422</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="1"/>
+      <c r="A6" s="1">
+        <v>1010050423</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="2">
+        <v>1010050424</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>1010050425</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>1010050426</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>1010050427</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>1010050428</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>1010050429</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>1010050430</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>1010050431</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>1010050432</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="1"/>
+      <c r="A16" s="1">
+        <v>1010050433</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="1"/>
+      <c r="A17" s="1">
+        <v>1010050434</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="1"/>
+      <c r="A18" s="1">
+        <v>1010050435</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1"/>
+      <c r="A19" s="1">
+        <v>1010050436</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1"/>
@@ -454,6 +497,33 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+      <c r="A26" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+      <c r="A27" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+      <c r="A28" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
+      <c r="A29" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
+      <c r="A30" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
+      <c r="A31" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+      <c r="A32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
